--- a/docs/test_scores.xlsx
+++ b/docs/test_scores.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="11964" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="classes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="classes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
@@ -1032,13 +1032,13 @@
         </is>
       </c>
       <c r="C2" s="0" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>78</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>45</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
@@ -1053,13 +1053,13 @@
         </is>
       </c>
       <c r="C3" s="0" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C4" s="0" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="C5" s="0" t="n">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -1116,13 +1116,13 @@
         </is>
       </c>
       <c r="C6" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
@@ -1140,10 +1140,10 @@
         <v>79</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="C8" s="0" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="C9" s="0" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="C10" s="0" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11">
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C11" s="0" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12">
@@ -1242,13 +1242,13 @@
         </is>
       </c>
       <c r="C12" s="0" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C13" s="0" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="C14" s="0" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E14" s="0" t="n">
         <v>52</v>
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="C15" s="0" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="C16" s="0" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>99</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17">
@@ -1347,13 +1347,13 @@
         </is>
       </c>
       <c r="C17" s="0" t="n">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>40</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18">
@@ -1368,13 +1368,13 @@
         </is>
       </c>
       <c r="C18" s="0" t="n">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19">
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="C19" s="0" t="n">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20">
@@ -1410,13 +1410,13 @@
         </is>
       </c>
       <c r="C20" s="0" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>81</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="C21" s="0" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22">
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="C22" s="0" t="n">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>78</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="C23" s="0" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="E23" s="0" t="n">
         <v>48</v>
@@ -1494,13 +1494,13 @@
         </is>
       </c>
       <c r="C24" s="0" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25">
@@ -1518,10 +1518,10 @@
         <v>90</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26">
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="C26" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27">
@@ -1557,13 +1557,13 @@
         </is>
       </c>
       <c r="C27" s="0" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="C28" s="0" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29">
@@ -1599,13 +1599,13 @@
         </is>
       </c>
       <c r="C29" s="0" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="E29" s="0" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30">
@@ -1620,13 +1620,13 @@
         </is>
       </c>
       <c r="C30" s="0" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E30" s="0" t="n">
-        <v>74</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31">
@@ -1641,13 +1641,13 @@
         </is>
       </c>
       <c r="C31" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="D31" s="0" t="n">
         <v>56</v>
       </c>
-      <c r="D31" s="0" t="n">
-        <v>46</v>
-      </c>
       <c r="E31" s="0" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32">
@@ -1662,13 +1662,13 @@
         </is>
       </c>
       <c r="C32" s="0" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="E32" s="0" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33">
@@ -1683,13 +1683,13 @@
         </is>
       </c>
       <c r="C33" s="0" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="E33" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34">
@@ -1704,13 +1704,13 @@
         </is>
       </c>
       <c r="C34" s="0" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E34" s="0" t="n">
-        <v>59</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35">
@@ -1725,13 +1725,13 @@
         </is>
       </c>
       <c r="C35" s="0" t="n">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="E35" s="0" t="n">
-        <v>87</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36">
@@ -1746,13 +1746,13 @@
         </is>
       </c>
       <c r="C36" s="0" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E36" s="0" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37">
@@ -1767,13 +1767,13 @@
         </is>
       </c>
       <c r="C37" s="0" t="n">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E37" s="0" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38">
@@ -1788,13 +1788,13 @@
         </is>
       </c>
       <c r="C38" s="0" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="D38" s="0" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E38" s="0" t="n">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39">
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="C39" s="0" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="E39" s="0" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="C40" s="0" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="E40" s="0" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41">
@@ -1851,13 +1851,13 @@
         </is>
       </c>
       <c r="C41" s="0" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="E41" s="0" t="n">
-        <v>74</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
